--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:34</t>
+    <t xml:space="preserve">2026-09-09 23:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:32</t>
+    <t xml:space="preserve">2026-09-17 14:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2022_la araucania.xlsx
@@ -96,12 +96,12 @@
     <t xml:space="preserve">Padre Las Casas</t>
   </si>
   <si>
+    <t xml:space="preserve">Lautaro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Victoria</t>
   </si>
   <si>
-    <t xml:space="preserve">Lautaro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lumaco</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:27</t>
+    <t xml:space="preserve">2026-09-23 12:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -911,7 +911,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>9211</v>
+        <v>9108</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2022</v>
@@ -928,7 +928,7 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>9108</v>
+        <v>9211</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2022</v>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2022_la araucania.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:54</t>
+    <t xml:space="preserve">2026-10-01 23:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -159,7 +159,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre salario mínimo (%)</t>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -172,9 +172,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre salario mínimo</t>
   </si>
 </sst>
 </file>
@@ -1184,7 +1181,7 @@
         <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:22</t>
+    <t xml:space="preserve">2026-10-02 11:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:27</t>
+    <t xml:space="preserve">2026-10-02 15:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:17</t>
+    <t xml:space="preserve">2026-10-05 12:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
